--- a/artfynd/A 15297-2022 artfynd.xlsx
+++ b/artfynd/A 15297-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121566392</v>
       </c>
       <c r="B2" t="n">
-        <v>90731</v>
+        <v>90739</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 15297-2022 artfynd.xlsx
+++ b/artfynd/A 15297-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121566392</v>
       </c>
       <c r="B2" t="n">
-        <v>90739</v>
+        <v>90753</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 15297-2022 artfynd.xlsx
+++ b/artfynd/A 15297-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121566392</v>
       </c>
       <c r="B2" t="n">
-        <v>90753</v>
+        <v>90755</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 15297-2022 artfynd.xlsx
+++ b/artfynd/A 15297-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,117 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123355298</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91520</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1143</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blekticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Haploporus tuberculosus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Niemelä &amp; Y.C.Dai</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bennebol, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>687711</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6652846</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15297-2022 artfynd.xlsx
+++ b/artfynd/A 15297-2022 artfynd.xlsx
@@ -820,6 +820,8 @@
           <t>dm²</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bennebol, Upl</t>
@@ -856,12 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,6 +872,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15297-2022 artfynd.xlsx
+++ b/artfynd/A 15297-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>123355298</v>
       </c>
       <c r="B3" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 15297-2022 artfynd.xlsx
+++ b/artfynd/A 15297-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>123355298</v>
       </c>
       <c r="B3" t="n">
-        <v>91523</v>
+        <v>91525</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 15297-2022 artfynd.xlsx
+++ b/artfynd/A 15297-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -889,6 +889,210 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123476314</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90917</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bennebol, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>687724</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6652795</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123476281</v>
+      </c>
+      <c r="B5" t="n">
+        <v>94859</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bennebol, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>687724</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6652795</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15297-2022 artfynd.xlsx
+++ b/artfynd/A 15297-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>123355298</v>
       </c>
       <c r="B3" t="n">
-        <v>91525</v>
+        <v>91531</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123476314</v>
+        <v>123476281</v>
       </c>
       <c r="B4" t="n">
-        <v>90917</v>
+        <v>94865</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,25 +903,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5445</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123476281</v>
+        <v>123476314</v>
       </c>
       <c r="B5" t="n">
-        <v>94859</v>
+        <v>90923</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2671</v>
+        <v>5445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 15297-2022 artfynd.xlsx
+++ b/artfynd/A 15297-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>123355298</v>
       </c>
       <c r="B3" t="n">
-        <v>91534</v>
+        <v>91551</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123476314</v>
+        <v>123476281</v>
       </c>
       <c r="B4" t="n">
-        <v>90926</v>
+        <v>94885</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,25 +903,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5445</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123476281</v>
+        <v>123476314</v>
       </c>
       <c r="B5" t="n">
-        <v>94868</v>
+        <v>90943</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2671</v>
+        <v>5445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 15297-2022 artfynd.xlsx
+++ b/artfynd/A 15297-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>123355298</v>
       </c>
       <c r="B3" t="n">
-        <v>91551</v>
+        <v>91556</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>123476281</v>
       </c>
       <c r="B4" t="n">
-        <v>94885</v>
+        <v>94891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>123476314</v>
       </c>
       <c r="B5" t="n">
-        <v>90943</v>
+        <v>90948</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 15297-2022 artfynd.xlsx
+++ b/artfynd/A 15297-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>123355298</v>
       </c>
       <c r="B3" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123476281</v>
+        <v>123476314</v>
       </c>
       <c r="B4" t="n">
-        <v>94891</v>
+        <v>90950</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,25 +903,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>5445</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123476314</v>
+        <v>123476281</v>
       </c>
       <c r="B5" t="n">
-        <v>90948</v>
+        <v>94893</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5445</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 15297-2022 artfynd.xlsx
+++ b/artfynd/A 15297-2022 artfynd.xlsx
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123476314</v>
+        <v>123476281</v>
       </c>
       <c r="B4" t="n">
-        <v>90950</v>
+        <v>95401</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,25 +903,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5445</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123476281</v>
+        <v>123476314</v>
       </c>
       <c r="B5" t="n">
-        <v>94893</v>
+        <v>90950</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2671</v>
+        <v>5445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 15297-2022 artfynd.xlsx
+++ b/artfynd/A 15297-2022 artfynd.xlsx
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123476281</v>
+        <v>123476314</v>
       </c>
       <c r="B4" t="n">
-        <v>95401</v>
+        <v>90950</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,25 +903,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>5445</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123476314</v>
+        <v>123476281</v>
       </c>
       <c r="B5" t="n">
-        <v>90950</v>
+        <v>95401</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5445</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 15297-2022 artfynd.xlsx
+++ b/artfynd/A 15297-2022 artfynd.xlsx
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123476314</v>
+        <v>123476281</v>
       </c>
       <c r="B4" t="n">
-        <v>90950</v>
+        <v>95401</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,25 +903,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5445</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123476281</v>
+        <v>123476314</v>
       </c>
       <c r="B5" t="n">
-        <v>95401</v>
+        <v>90950</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2671</v>
+        <v>5445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 15297-2022 artfynd.xlsx
+++ b/artfynd/A 15297-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121566392</v>
+        <v>109101857</v>
       </c>
       <c r="B2" t="n">
-        <v>90755</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75316</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>93</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ekpricklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Inoderma byssaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Weigel) Gray</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ekdalen, Upl</t>
+          <t>Ekdalens NR, 200 m V parkeringen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>687466</v>
+        <v>687260</v>
       </c>
       <c r="R2" t="n">
-        <v>6652870</v>
+        <v>6652935</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2023-05-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2023-05-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,33 +765,44 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Rikard Anderberg, Maya Edlund, Ossian Rydebjörk, Stina Hällholm, Malin Löfgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123355298</v>
+        <v>109101935</v>
       </c>
       <c r="B3" t="n">
-        <v>91580</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,48 +810,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1143</v>
+        <v>94</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blekticka</t>
+          <t>Puderfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus tuberculosus</t>
+          <t>Arthonia cinereopruinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä &amp; Y.C.Dai</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Schaer.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bennebol, Upl</t>
+          <t>Ekdalens NR, 150 m V parkeringen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687711</v>
+        <v>687300</v>
       </c>
       <c r="R3" t="n">
-        <v>6652846</v>
+        <v>6652945</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,12 +867,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2023-05-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2023-05-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,68 +885,85 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Malin Löfgren, Stina Hällholm, Ossian Rydebjörk, Maya Edlund, Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123476281</v>
+        <v>109101914</v>
       </c>
       <c r="B4" t="n">
-        <v>95423</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81531</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>145</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klosterlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Biatoridium monasteriense</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>J.Lahm ex Körb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bennebol, Upl</t>
+          <t>Ekdalens NR, 200 m V parkeringen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687724</v>
+        <v>687270</v>
       </c>
       <c r="R4" t="n">
-        <v>6652795</v>
+        <v>6652935</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,12 +987,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2023-05-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2023-05-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,68 +1001,79 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Malin Löfgren, Stina Hällholm, Ossian Rydebjörk, Maya Edlund, Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123476314</v>
+        <v>122463707</v>
       </c>
       <c r="B5" t="n">
-        <v>90972</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81531</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5445</v>
+        <v>145</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Klosterlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Biatoridium monasteriense</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>J.Lahm ex Körb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bennebol, Upl</t>
+          <t>Ekdalen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687724</v>
+        <v>687267</v>
       </c>
       <c r="R5" t="n">
-        <v>6652795</v>
+        <v>6652934</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1100,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1079,6 +1116,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1088,10 +1140,4968 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
+          <t>Viktor Lund, Cajsa Björkén, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122463696</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78739</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>218</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ekspik</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Calicium quercinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ekdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>687255</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6652939</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På Cliostomum corrugatum på mycket grov ek intill Chaenotheca cinerea</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Viktor Lund, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122463698</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83294</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>307</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blekskaftad nållav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chaenotheca cinerea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Pers.) Tibell</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ekdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>687255</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6652939</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På grov ek intill Calicium quercinum</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Viktor Lund, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125405945</v>
+      </c>
+      <c r="B8" t="n">
+        <v>83294</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>307</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blekskaftad nållav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chaenotheca cinerea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Pers.) Tibell</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>687256</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6652935</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Åke Berg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Åke Berg, Cajsa Björkén, Martin Westberg, Ola Hammarström, Niklas Hjort, Björn Bråvander, Majken Ekstrand, Didrik Vanhoenacker, Rasmus Elleby, Karin Wiklund, Clara Lerbro, Signe Vendike, Carin von Köhler, Alexander Hoffmann, Niina Sallmén, Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>109101884</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79795</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>374</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gul dropplav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cliostomum corrugatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, 200 m V parkeringen, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>687260</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6652935</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg, Maya Edlund, Ossian Rydebjörk, Stina Hällholm, Malin Löfgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125405964</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79795</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>374</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gul dropplav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cliostomum corrugatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>687256</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6652935</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Åke Berg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Åke Berg, Cajsa Björkén, Martin Westberg, Ola Hammarström, Niklas Hjort, Björn Bråvander, Majken Ekstrand, Didrik Vanhoenacker, Rasmus Elleby, Karin Wiklund, Clara Lerbro, Signe Vendike, Carin von Köhler, Alexander Hoffmann, Niina Sallmén, Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125405952</v>
+      </c>
+      <c r="B11" t="n">
+        <v>75341</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1114</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gammelekslav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lecanographa amylacea</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>687256</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6652935</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Åke Berg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Åke Berg, Cajsa Björkén, Martin Westberg, Ola Hammarström, Niklas Hjort, Björn Bråvander, Majken Ekstrand, Didrik Vanhoenacker, Rasmus Elleby, Karin Wiklund, Clara Lerbro, Signe Vendike, Carin von Köhler, Alexander Hoffmann, Niina Sallmén, Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>75073829</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92510</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1143</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blekticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Haploporus tuberculosus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Niemelä &amp; Y.C.Dai</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>687340</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6652947</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2000-06-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2000-06-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På bark på grov, levande ek.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark på grov, levande ek. # Skogsek</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123355298</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92510</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1143</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blekticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Haploporus tuberculosus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Niemelä &amp; Y.C.Dai</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bennebol, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>687711</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6652846</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Viktor Lund</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121566392</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91920</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ekdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>687466</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6652870</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>74810593</v>
+      </c>
+      <c r="B15" t="n">
+        <v>83312</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>687340</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6652947</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2000-06-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2000-06-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På stammen av grov, levande ek.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stammen av grov, levande ek. # Skogsek</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>109101861</v>
+      </c>
+      <c r="B16" t="n">
+        <v>83312</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, 200 m V parkeringen, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>687260</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6652935</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg, Maya Edlund, Ossian Rydebjörk, Stina Hällholm, Malin Löfgren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>109101949</v>
+      </c>
+      <c r="B17" t="n">
+        <v>83312</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, ekbryn V parkeringen, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>687345</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6652945</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Malin Löfgren, Stina Hällholm, Ossian Rydebjörk, Maya Edlund, Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121571323</v>
+      </c>
+      <c r="B18" t="n">
+        <v>83312</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ekdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>687279</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6652942</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125405972</v>
+      </c>
+      <c r="B19" t="n">
+        <v>83312</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>687256</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6652935</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Åke Berg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Åke Berg, Cajsa Björkén, Martin Westberg, Ola Hammarström, Niklas Hjort, Björn Bråvander, Majken Ekstrand, Didrik Vanhoenacker, Rasmus Elleby, Karin Wiklund, Clara Lerbro, Signe Vendike, Carin von Köhler, Alexander Hoffmann, Niina Sallmén, Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>109101912</v>
+      </c>
+      <c r="B20" t="n">
+        <v>77750</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1766</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Slät fjällav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Agonimia allobata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Stizenb.) P.James</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med perithecier</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, 200 m V parkeringen, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>687270</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6652935</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Malin Löfgren, Stina Hällholm, Ossian Rydebjörk, Maya Edlund, Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>109102001</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93136</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2075</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rutskinn</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Xylobolus frustulatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Boidin</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, N parkeringen, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>687425</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6652925</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg, Maya Edlund, Ossian Rydebjörk, Stina Hällholm, Malin Löfgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125405983</v>
+      </c>
+      <c r="B22" t="n">
+        <v>93136</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2075</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rutskinn</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Xylobolus frustulatus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Boidin</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>687256</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6652935</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Åke Berg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Åke Berg, Cajsa Björkén, Martin Westberg, Ola Hammarström, Niklas Hjort, Björn Bråvander, Majken Ekstrand, Didrik Vanhoenacker, Rasmus Elleby, Karin Wiklund, Clara Lerbro, Signe Vendike, Carin von Köhler, Alexander Hoffmann, Niina Sallmén, Dennis Nyström, Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>6920179</v>
+      </c>
+      <c r="B23" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ekdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>687268</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6652941</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2013-08-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2013-08-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123354482</v>
+      </c>
+      <c r="B24" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bennebol, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>687693</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6652900</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>123476281</v>
+      </c>
+      <c r="B25" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bennebol, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>687724</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6652795</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125406026</v>
+      </c>
+      <c r="B26" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>687256</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6652935</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Åke Berg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Åke Berg, Cajsa Björkén, Martin Westberg, Ola Hammarström, Niklas Hjort, Björn Bråvander, Majken Ekstrand, Didrik Vanhoenacker, Rasmus Elleby, Karin Wiklund, Clara Lerbro, Signe Vendike, Carin von Köhler, Alexander Hoffmann, Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>109101863</v>
+      </c>
+      <c r="B27" t="n">
+        <v>96183</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2674</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Liten baronmossa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Anomodon longifolius</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schleich. ex Brid.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, 200 m V parkeringen, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>687260</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6652935</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg, Maya Edlund, Ossian Rydebjörk, Stina Hällholm, Malin Löfgren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121570997</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91502</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>3086</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svartöra</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Auricularia mesenterica</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Dicks.:Fr.) Pers.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ekdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>687311</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6652950</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>123475943</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91893</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bennebol, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>687740</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6652961</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>123353808</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bennebol, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>687690</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6652918</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>123354471</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91867</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bennebol, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>687693</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6652900</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>123476314</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91867</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bennebol, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>687724</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6652795</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>121571338</v>
+      </c>
+      <c r="B33" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ekdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>687279</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6652942</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>109101990</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79707</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, N parkeringen, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>687425</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6652925</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Malin Löfgren, Stina Hällholm, Ossian Rydebjörk, Maya Edlund, Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>109101887</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78728</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6436</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Gulpudrad spiklav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Calicium adspersum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, 200 m V parkeringen, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>687260</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6652935</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg, Maya Edlund, Ossian Rydebjörk, Stina Hällholm, Malin Löfgren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>109101978</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78728</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6436</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Gulpudrad spiklav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Calicium adspersum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, ekbryn V parkeringen, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>687365</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6652945</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Malin Löfgren, Stina Hällholm, Ossian Rydebjörk, Maya Edlund, Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125405975</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78728</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6436</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Gulpudrad spiklav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Calicium adspersum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>687256</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6652935</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Åke Berg</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Åke Berg, Cajsa Björkén, Martin Westberg, Ola Hammarström, Niklas Hjort, Björn Bråvander, Majken Ekstrand, Didrik Vanhoenacker, Rasmus Elleby, Karin Wiklund, Clara Lerbro, Signe Vendike, Carin von Köhler, Alexander Hoffmann, Niina Sallmén, Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>123354075</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78685</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6443</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Sotlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Acolium inquinans</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Bennebol, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>687690</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6652918</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Inuti ett utkarvat hål tvärs genom stammen på död tall.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>109101973</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80367</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6457</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Scytinium teretiusculum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, ekbryn V parkeringen, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>687365</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6652945</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Malin Löfgren, Stina Hällholm, Ossian Rydebjörk, Maya Edlund, Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>109101971</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, ekbryn V parkeringen, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>687365</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6652945</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Malin Löfgren, Stina Hällholm, Ossian Rydebjörk, Maya Edlund, Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>109101997</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, N parkeringen, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>687425</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6652925</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg, Maya Edlund, Ossian Rydebjörk, Stina Hällholm, Malin Löfgren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>122463708</v>
+      </c>
+      <c r="B42" t="n">
+        <v>83314</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6471</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gulvit blekspik</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Sclerophora pallida</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Ekdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>687267</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6652934</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Cajsa Björkén, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>125406008</v>
+      </c>
+      <c r="B43" t="n">
+        <v>83314</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6471</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gulvit blekspik</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Sclerophora pallida</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>687256</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6652935</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Åke Berg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Åke Berg, Cajsa Björkén, Martin Westberg, Ola Hammarström, Niklas Hjort, Björn Bråvander, Majken Ekstrand, Didrik Vanhoenacker, Rasmus Elleby, Karin Wiklund, Clara Lerbro, Signe Vendike, Carin von Köhler, Alexander Hoffmann, Niina Sallmén, Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>75726820</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57811</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100137</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Slaguggla</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Strix uralensis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Pallas, 1771</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Ekdalens naturreservat, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>687319</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6652932</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>1999-02-13</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>1999-02-13</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Pär Eriksson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Pär Eriksson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>109101878</v>
+      </c>
+      <c r="B45" t="n">
+        <v>9363</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>101254</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Skeppsvarvsfluga</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lymexylon navale</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, 200 m V parkeringen, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>687260</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6652935</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg, Maya Edlund, Ossian Rydebjörk, Stina Hällholm, Malin Löfgren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>123353878</v>
+      </c>
+      <c r="B46" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Bennebol, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>687690</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6652918</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>117818433</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>687438</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6652911</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>124410940</v>
+      </c>
+      <c r="B48" t="n">
+        <v>61491</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>106670</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Svart skogssnigel</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Arion ater ater</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Ekdalen NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>687432</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6652913</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>121431042</v>
+      </c>
+      <c r="B49" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Bennebols bruk, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>687459</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6652929</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist, Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>109101959</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Ekdalens NR, ekbryn V parkeringen, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>687345</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6652945</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Bladåker</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Malin Löfgren, Stina Hällholm, Ossian Rydebjörk, Maya Edlund, Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
